--- a/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
+++ b/deliverables/4-revenue-modeling/tools/Aurumix_Revenue_Model.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>REVENUE ONLY. Six revenue streams, reported net of cost of revenue. Operating costs, tax, cash and funding are added in a later build.</t>
+          <t>Six revenue streams at their full charge, with the fabrication premium as cost of goods sold, plus the modelled cost base, net profit, unit economics, regulatory capital, the float and the peak funding need. Headcount and tax are not yet in the cost base, so every profit figure is an upper bound.</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
     <row r="25">
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Kept as inputs rather than engines: card eligibility (% who qualify, months to qualify), the holders balance, and the fabrication premium inside stream 1.</t>
+          <t>Kept as inputs rather than engines: the holders balance, the fabrication premium inside stream 1, and the ICS qualification rate (a memo that prices benefits; it no longer gates the card).</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NOBODY HAS DECIDED THIS. It determines whether the card streams - the majority of revenue - decay with churn or are immune to it. Worth a 42% swing in terminal revenue. Default ON because nothing in the design revokes the card; report both.</t>
+          <t>DECIDED 2026-09-22 (decision 54): a customer who stops paying keeps the card and the credit line; only the collateral ladder, the customer or the lender can close them. So ON is the design, and the card streams do not decay with churn. OFF is kept as a sensitivity: recalculated 2026-09-24, it takes Y7 revenue from USD 4.49m to 3.88m (-13.7%) and streams 2, 4 and 5 together down 58%.</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>NOBODY HAS DECIDED THIS. It determines whether the card streams - the majority of revenue - decay with churn or are immune to it. Worth a 42% swing in terminal revenue. Default ON because nothing in the design revokes the card; report both.</t>
+          <t>DECIDED 2026-09-22 (decision 54): a customer who stops paying keeps the card and the credit line; only the collateral ladder, the customer or the lender can close them. So ON is the design, and the card streams do not decay with churn. OFF is kept as a sensitivity: recalculated 2026-09-24, it takes Y7 revenue from USD 4.49m to 3.88m (-13.7%) and streams 2, 4 and 5 together down 58%.</t>
         </is>
       </c>
     </row>
@@ -44702,7 +44702,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>REVENUE ONLY. Operating costs, tax, working capital, cash and funding are added in a later build, so there is no profit or break-even line here. Stream 1 IS reported net of the fabrication premium, because that is cost OF REVENUE rather than an operating cost - reporting it gross would read ~43% high.</t>
+          <t>Headcount and tax are not yet in the cost base, so net profit and payback are upper bounds. Stream 1 is shown at the full entry fee; the fabrication premium paid to the dealer sits in the cost base as cost of goods sold. Read on its own, the gross fee overstates what Aurumix keeps by 29-39% of the net figure, depending on the year. Y1 and Y2 ratio rows (card cost share, contribution, payback) use the M12 and M24 month-end run rates, not annual totals.</t>
         </is>
       </c>
     </row>
